--- a/data/mock_100_已分析.xlsx
+++ b/data/mock_100_已分析.xlsx
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.67</v>
+        <v>0.703</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.67</v>
+        <v>0.679</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1163,15 +1163,15 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>客服态度差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.67</v>
+        <v>0.623</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>已读不回</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1181,22 +1181,22 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>您好，感谢您的反馈。关于“已读不回”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
+          <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>非常理解您的心情，已读不回确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
+          <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>哎呀让您踩坑了！已读不回这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
+          <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>bge</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.67</v>
+        <v>0.703</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.67</v>
+        <v>0.696</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1375,15 +1375,15 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>您好，感谢您的反馈。关于“质量差”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
+          <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>非常理解您的心情，质量差确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
+          <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>哎呀让您踩坑了！质量差这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
+          <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>bge</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.67</v>
+        <v>0.741</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.67</v>
+        <v>0.696</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2064,15 +2064,15 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.35</v>
+        <v>0.665</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2082,22 +2082,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>您好，感谢您的反馈。关于“质量差”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
+          <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>非常理解您的心情，质量差确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
+          <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>哎呀让您踩坑了！质量差这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
+          <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>bge</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.67</v>
+        <v>0.678</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.67</v>
+        <v>0.716</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.67</v>
+        <v>0.671</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.67</v>
+        <v>0.696</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.67</v>
+        <v>0.722</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -3124,15 +3124,15 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>客服态度差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>已读不回</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -3142,22 +3142,22 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>您好，感谢您的反馈。关于“已读不回”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
+          <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>非常理解您的心情，已读不回确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
+          <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>哎呀让您踩坑了！已读不回这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
+          <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>bge</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -3230,15 +3230,15 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.67</v>
+        <v>0.636</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3248,22 +3248,22 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>您好，感谢您的反馈。关于“质量差”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
+          <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>非常理解您的心情，质量差确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
+          <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>哎呀让您踩坑了！质量差这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
+          <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>bge</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -3336,15 +3336,15 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.35</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3354,22 +3354,22 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>您好，感谢您的反馈。关于“质量差”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
+          <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>非常理解您的心情，质量差确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
+          <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>哎呀让您踩坑了！质量差这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
+          <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>bge</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.67</v>
+        <v>0.706</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.67</v>
+        <v>0.677</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -3866,15 +3866,15 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>客服态度差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.67</v>
+        <v>0.641</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>客服态度差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3884,22 +3884,22 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>您好，感谢您的反馈。关于“客服态度差”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
+          <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>非常理解您的心情，客服态度差确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
+          <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>哎呀让您踩坑了！客服态度差这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
+          <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>bge</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.67</v>
+        <v>0.678</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4555,15 +4555,15 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>客服态度差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>客服态度差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4573,22 +4573,22 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>您好，感谢您的反馈。关于“客服态度差”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
+          <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>非常理解您的心情，客服态度差确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
+          <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>哎呀让您踩坑了！客服态度差这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
+          <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>bge</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0.67</v>
+        <v>0.675</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.79</v>
+        <v>0.791</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -4926,15 +4926,15 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>0.67</v>
+        <v>0.649</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4944,22 +4944,22 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>您好，感谢您的反馈。关于“质量差”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
+          <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>非常理解您的心情，质量差确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
+          <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>哎呀让您踩坑了！质量差这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
+          <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>bge</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>0.35</v>
+        <v>0.573</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>0.35</v>
+        <v>0.556</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>hybrid-agree</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"质量差": 30, "客服态度差": 24, "物流慢": 25, "货不对版": 21}</t>
+          <t>{"质量差": 25, "客服态度差": 20, "物流慢": 25, "货不对版": 30}</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>88.0%</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>10.83</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.108</t>
         </is>
       </c>
     </row>

--- a/data/mock_100_已分析.xlsx
+++ b/data/mock_100_已分析.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析结果" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工复核" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'分析结果'!$A$1:$K$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'分析结果'!$A$1:$M$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +39,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="002F5597"/>
         <bgColor rgb="002F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,12 +71,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -438,20 +448,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -487,25 +499,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>归因方法</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>证据</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>需人工复核</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>官方回复</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>共情回复</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>幽默回复</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>方法</t>
         </is>
@@ -540,27 +562,37 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>零件有瑕疵，螺丝都拧不紧 不会再买了</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“瑕疵”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，瑕疵确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！瑕疵这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -584,7 +616,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.91</v>
+        <v>0.997</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -593,27 +625,37 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>客服半天不回，回了就是机器人话术 真的很失望</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“机器人”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，机器人确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！机器人这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -646,27 +688,37 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>投诉也没用，回复全是模板 希望改进</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“模板”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，模板确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！模板这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -690,7 +742,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.79</v>
+        <v>0.875</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -699,27 +751,37 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>物流慢就算了，还发错地址了 真的很失望</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -752,27 +814,37 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>款式和直播间展示的不一样</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -805,25 +877,35 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>承诺退款，三天了还没到账 不会再买了</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“客服态度差”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，客服态度差确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！客服态度差这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -858,27 +940,37 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>投诉也没用，回复全是模板 真的很失望</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“模板”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，模板确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！模板这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -902,7 +994,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.79</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -911,27 +1003,37 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>图片是红色，发来是暗红，色差太大 体验很差</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“色差”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，色差确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！色差这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -964,27 +1066,37 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>晚上9点后客服直接离线，找不到人 希望改进</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“客服态度差”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，客服态度差确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！客服态度差这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1120,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1017,27 +1129,37 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>颜色和主图完全不符，实物很土 体验很差</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1070,27 +1192,37 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>以为是两件装，结果只有一件 已申请退货</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1123,27 +1255,37 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>双十一买的，比别人晚到一周 希望改进</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“晚到”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，晚到确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！晚到这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1176,27 +1318,37 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>不给开发票，问多了就已读不回 已申请退货</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>bge</t>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>bge-rerank</t>
         </is>
       </c>
     </row>
@@ -1229,27 +1381,37 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>零件有瑕疵，螺丝都拧不紧 不会再买了</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“瑕疵”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，瑕疵确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！瑕疵这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1282,25 +1444,35 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>承诺退款，三天了还没到账 不会再买了</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“客服态度差”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，客服态度差确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！客服态度差这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -1335,27 +1507,37 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>物流信息三天不更新，以为丢件了 体验很差</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1388,27 +1570,37 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>跟详情页完全不一样，偷工减料 体验很差</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>bge</t>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>bge-rerank</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1624,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.79</v>
+        <v>0.944</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1441,27 +1633,37 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>用了两天就开线了，做工太差 希望改进</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“开线”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，开线确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！开线这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1687,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.741</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1494,27 +1696,37 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>接口松动，接触不良，品控不行</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“品控”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，品控确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！品控这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1547,27 +1759,37 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>尺码偏小一码，标的M实际是S 体验很差</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“尺码偏小”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，尺码偏小确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！尺码偏小这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1600,27 +1822,37 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>双十一买的，比别人晚到一周 已申请退货</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“晚到”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，晚到确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！晚到这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1653,27 +1885,37 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>物流信息三天不更新，以为丢件了 体验很差</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1693,40 +1935,50 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.35</v>
+        <v>0.619</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
           <t>买的大杯，到手是中杯，缺斤少两 不会再买了</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>您好，感谢您的反馈。关于“质量差”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>非常理解您的心情，质量差确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>哎呀让您踩坑了！质量差这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
+          <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>bge-rerank</t>
         </is>
       </c>
     </row>
@@ -1759,27 +2011,37 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>客服说不归他管，让我自己找厂家 不会再买了</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“客服态度差”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，客服态度差确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！客服态度差这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1803,7 +2065,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1812,27 +2074,37 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>客服半天不回，回了就是机器人话术 已申请退货</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“机器人”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，机器人确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！机器人这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1865,27 +2137,37 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>快递员不送上门，直接扔驿站还不通知 不会再买了</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“驿站”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，驿站确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！驿站这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -1918,78 +2200,98 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>下单后48小时才出库，等得花都谢了</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>语气很冲，好像我欠他钱一样 不会再买了</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>客服态度差</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>质量差</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>质量差</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>语气很冲，好像我欠他钱一样 不会再买了</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“质量差”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>非常理解您的心情，质量差确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！质量差这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -2024,27 +2326,37 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
           <t>描述是纯棉，标签写着聚酯纤维 真的很失望</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2077,27 +2389,37 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
           <t>跟详情页完全不一样，偷工减料 已申请退货</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>bge</t>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>bge-rerank</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2443,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.79</v>
+        <v>0.796</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2130,27 +2452,37 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
           <t>面料起球严重，洗一次就变形</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“起球”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，起球确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！起球这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2183,27 +2515,37 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
           <t>塑料感很强，一看就是廉价货 已申请退货</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“廉价”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，廉价确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！廉价这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2236,78 +2578,98 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
           <t>双十一买的，比别人晚到一周 真的很失望</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“晚到”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，晚到确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！晚到这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>语气很冲，好像我欠他钱一样 不会再买了</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>客服态度差</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>质量差</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>质量差</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>语气很冲，好像我欠他钱一样 不会再买了</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“质量差”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>非常理解您的心情，质量差确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！质量差这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="M35" s="3" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -2342,27 +2704,37 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
           <t>快递在路上走了4天，包装都压扁了 不会再买了</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2758,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.716</v>
+        <v>0.751</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2395,27 +2767,37 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
           <t>晚上9点后客服直接离线，找不到人 体验很差</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“客服态度差”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，客服态度差确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！客服态度差这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2821,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.79</v>
+        <v>0.874</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2448,27 +2830,37 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>面料起球严重，洗一次就变形 已申请退货</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“起球”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，起球确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！起球这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2488,40 +2880,50 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.35</v>
+        <v>0.614</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>质量差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
           <t>买的大杯，到手是中杯，缺斤少两 希望改进</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>您好，感谢您的反馈。关于“质量差”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
-        </is>
-      </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>非常理解您的心情，质量差确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>哎呀让您踩坑了！质量差这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
+          <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>bge-rerank</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2947,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.91</v>
+        <v>0.955</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2554,27 +2956,37 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
           <t>申请售后，客服一直推诿不处理 真的很失望</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“不处理”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，不处理确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！不处理这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2607,27 +3019,37 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
           <t>款式和直播间展示的不一样 希望改进</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2660,27 +3082,37 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
           <t>描述是纯棉，标签写着聚酯纤维 体验很差</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2713,27 +3145,37 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
           <t>和标题写的配置对不上，被骗了 已申请退货</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2757,7 +3199,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.79</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2766,27 +3208,37 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
           <t>颜色和主图完全不符，实物很土 真的很失望</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2819,27 +3271,37 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
           <t>外地仓发货，运费还贵，到得又慢 不会再买了</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2872,25 +3334,35 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
           <t>说好的送赠品，根本没有 已申请退货</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -2925,27 +3397,37 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
           <t>物流信息三天不更新，以为丢件了 体验很差</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -2969,7 +3451,7 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.79</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2978,27 +3460,37 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
           <t>图片是红色，发来是暗红，色差太大 体验很差</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“色差”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，色差确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！色差这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3514,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.722</v>
+        <v>0.694</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3031,27 +3523,37 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
           <t>接口松动，接触不良，品控不行 已申请退货</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“品控”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，品控确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！品控这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -3084,27 +3586,37 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
           <t>说好的送赠品，根本没有 希望改进</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -3137,27 +3649,37 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
           <t>不给开发票，问多了就已读不回 体验很差</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>bge</t>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>bge-rerank</t>
         </is>
       </c>
     </row>
@@ -3190,27 +3712,37 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
           <t>问尺寸，客服直接甩链接，态度敷衍 希望改进</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“敷衍”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，敷衍确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！敷衍这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -3243,27 +3775,37 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
           <t>收到就是坏的，退换还要自己出运费 真的很失望</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>bge</t>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>bge-rerank</t>
         </is>
       </c>
     </row>
@@ -3296,27 +3838,37 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
           <t>以为是两件装，结果只有一件 不会再买了</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -3349,27 +3901,37 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
           <t>跟详情页完全不一样，偷工减料 希望改进</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>bge</t>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>bge-rerank</t>
         </is>
       </c>
     </row>
@@ -3402,27 +3964,37 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
           <t>问尺寸，客服直接甩链接，态度敷衍 体验很差</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“敷衍”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，敷衍确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！敷衍这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -3455,27 +4027,37 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
           <t>材质很薄，风一吹就要散架 希望改进</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“薄”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，薄确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！薄这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -3508,27 +4090,37 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
           <t>描述是纯棉，标签写着聚酯纤维 希望改进</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -3561,25 +4153,35 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
           <t>说好补偿10元券，根本没发 不会再买了</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“客服态度差”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，客服态度差确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！客服态度差这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -3614,27 +4216,37 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
           <t>快递员不送上门，直接扔驿站还不通知 不会再买了</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“驿站”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，驿站确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！驿站这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -3667,27 +4279,37 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
           <t>快递在路上走了4天，包装都压扁了 体验很差</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -3720,27 +4342,37 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
           <t>说好的送赠品，根本没有</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -3773,78 +4405,98 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
           <t>零件有瑕疵，螺丝都拧不紧</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“瑕疵”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，瑕疵确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！瑕疵这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
     <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>味道很重，晾了三天还有甲醛味</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>质量差</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>质量差</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>甲醛</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>味道很重，晾了三天还有甲醛味</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“甲醛”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="K64" s="3" t="inlineStr">
         <is>
           <t>非常理解您的心情，甲醛确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="L64" s="3" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！甲醛这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="M64" s="3" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -3879,27 +4531,37 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
           <t>套餐里少了一件，客服说看错了 不会再买了</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>bge</t>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>bge-rerank</t>
         </is>
       </c>
     </row>
@@ -3932,25 +4594,35 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
           <t>不给开发票，问多了就已读不回</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“已读不回”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，已读不回确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！已读不回这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -3976,7 +4648,7 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.91</v>
+        <v>0.974</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3985,27 +4657,37 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
           <t>等了5天才到，物流太慢了 体验很差</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“等了”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，等了确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！等了这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4038,27 +4720,37 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
           <t>用了一周就掉色，质量堪忧 希望改进</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“掉色”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，掉色确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！掉色这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4091,27 +4783,37 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
           <t>物流慢就算了，还发错地址了</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4837,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.79</v>
+        <v>0.866</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4144,27 +4846,37 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
           <t>图片是红色，发来是暗红，色差太大 不会再买了</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“色差”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，色差确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！色差这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4197,27 +4909,37 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
           <t>外地仓发货，运费还贵，到得又慢 不会再买了</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="L71" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4250,27 +4972,37 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
           <t>快递在路上走了4天，包装都压扁了 不会再买了</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4303,27 +5035,37 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
           <t>问尺寸，客服直接甩链接，态度敷衍 不会再买了</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“敷衍”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，敷衍确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="L73" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！敷衍这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4356,27 +5098,37 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
           <t>尺码偏小一码，标的M实际是S 真的很失望</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“尺码偏小”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，尺码偏小确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！尺码偏小这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4409,27 +5161,37 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
           <t>催了客服三次才发货，物流蜗牛 已申请退货</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="L75" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4462,27 +5224,37 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
           <t>尺码偏小一码，标的M实际是S</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“尺码偏小”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，尺码偏小确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！尺码偏小这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4515,27 +5287,37 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
           <t>塑料感很强，一看就是廉价货 已申请退货</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“廉价”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，廉价确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="L77" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！廉价这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4568,27 +5350,37 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
           <t>套餐里少了一件，客服说看错了</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="L78" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>bge</t>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>bge-rerank</t>
         </is>
       </c>
     </row>
@@ -4612,7 +5404,7 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0.675</v>
+        <v>0.757</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4621,27 +5413,37 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
           <t>客服说不归他管，让我自己找厂家 真的很失望</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“客服态度差”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，客服态度差确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！客服态度差这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4665,7 +5467,7 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4674,27 +5476,37 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
           <t>用了两天就开线了，做工太差 已申请退货</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“开线”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，开线确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="L80" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！开线这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4718,7 +5530,7 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.791</v>
+        <v>0.957</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4727,27 +5539,37 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
           <t>用了两天就开线了，做工太差</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“开线”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，开线确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="L81" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！开线这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4771,7 +5593,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0.79</v>
+        <v>0.796</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4780,27 +5602,37 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
           <t>面料起球严重，洗一次就变形</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“起球”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，起球确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！起球这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4824,7 +5656,7 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.91</v>
+        <v>0.914</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4833,27 +5665,37 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
           <t>用了一周就掉色，质量堪忧 真的很失望</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“掉色”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，掉色确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="L83" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！掉色这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4877,7 +5719,7 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4886,27 +5728,37 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
           <t>发货慢，三天才揽收，急用耽误事了 不会再买了</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“发货慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，发货慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr">
+      <c r="L84" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！发货慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -4939,27 +5791,37 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
           <t>收到就是坏的，退换还要自己出运费 体验很差</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>bge</t>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>bge-rerank</t>
         </is>
       </c>
     </row>
@@ -4983,7 +5845,7 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0.91</v>
+        <v>0.944</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -4992,78 +5854,98 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
           <t>发货慢，三天才揽收，急用耽误事了 希望改进</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“发货慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，发货慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
+      <c r="L86" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！发货慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
     <row r="87" ht="32" customHeight="1">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>语气很冲，好像我欠他钱一样</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>客服态度差</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>质量差</t>
         </is>
       </c>
-      <c r="E87" s="2" t="n">
+      <c r="E87" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>质量差</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>语气很冲，好像我欠他钱一样</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“质量差”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="K87" s="3" t="inlineStr">
         <is>
           <t>非常理解您的心情，质量差确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
+      <c r="L87" s="3" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！质量差这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="M87" s="3" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -5098,27 +5980,37 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
           <t>味道很重，晾了三天还有甲醛味 体验很差</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“甲醛”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="K88" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，甲醛确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！甲醛这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -5138,40 +6030,50 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>客服态度差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0.67</v>
+        <v>0.615</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>客服态度差</t>
+          <t>货不对版</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
           <t>说好补偿10元券，根本没发 体验很差</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>您好，感谢您的反馈。关于“客服态度差”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
-        </is>
-      </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>非常理解您的心情，客服态度差确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>哎呀让您踩坑了！客服态度差这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
+          <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>bge-rerank</t>
         </is>
       </c>
     </row>
@@ -5195,7 +6097,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0.91</v>
+        <v>0.924</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5204,27 +6106,37 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
           <t>申请售后，客服一直推诿不处理</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“不处理”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，不处理确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="L90" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！不处理这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -5248,7 +6160,7 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5257,27 +6169,37 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
           <t>客服半天不回，回了就是机器人话术 不会再买了</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“机器人”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，机器人确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="L91" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！机器人这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -5310,27 +6232,37 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
           <t>催了客服三次才发货，物流蜗牛 体验很差</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr">
+      <c r="L92" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -5363,27 +6295,37 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
           <t>味道很重，晾了三天还有甲醛味 真的很失望</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“甲醛”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="K93" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，甲醛确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="L93" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！甲醛这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -5407,7 +6349,7 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5416,27 +6358,37 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
           <t>等了5天才到，物流太慢了 不会再买了</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“等了”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="K94" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，等了确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="L94" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！等了这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -5469,27 +6421,37 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
           <t>款式和直播间展示的不一样 真的很失望</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="L95" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -5513,7 +6475,7 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>0.91</v>
+        <v>0.969</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5522,27 +6484,37 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
           <t>等了5天才到，物流太慢了 真的很失望</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“等了”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
+      <c r="K96" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，等了确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="L96" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！等了这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -5575,27 +6547,37 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
           <t>下单后48小时才出库，等得花都谢了 真的很失望</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“物流慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，物流慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr">
+      <c r="L97" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！物流慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -5628,27 +6610,37 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
           <t>和标题写的配置对不上，被骗了</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“货不对版”问题，我们已记录并将核对仓储记录并补发正确商品，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="K98" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，货不对版确实让人失望。我们已加急处理，会核对仓储记录并补发正确商品，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr">
+      <c r="L98" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！货不对版这锅我们背，已安排核对仓储记录并补发正确商品，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -5681,27 +6673,37 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
           <t>材质很薄，风一吹就要散架 不会再买了</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“薄”问题，我们已记录并将安排质检复核并支持免费换新/退货，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，薄确实让人失望。我们已加急处理，会安排质检复核并支持免费换新/退货，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="L99" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！薄这锅我们背，已安排安排质检复核并支持免费换新/退货，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -5725,7 +6727,7 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0.91</v>
+        <v>0.944</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5734,27 +6736,37 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
           <t>发货慢，三天才揽收，急用耽误事了 希望改进</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“发货慢”问题，我们已记录并将催促物流并为您补偿一张运费券，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，发货慢确实让人失望。我们已加急处理，会催促物流并为您补偿一张运费券，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="L100" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！发货慢这锅我们背，已安排催促物流并为您补偿一张运费券，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
@@ -5778,7 +6790,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0.91</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5787,32 +6799,42 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
           <t>申请售后，客服一直推诿不处理 不会再买了</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
         <is>
           <t>您好，感谢您的反馈。关于“不处理”问题，我们已记录并将对客服进行培训并由主管1小时内回访您，给您带来不便深表歉意，感谢您的监督。</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>非常理解您的心情，不处理确实让人失望。我们已加急处理，会对客服进行培训并由主管1小时内回访您，希望能再给我们一次弥补的机会～</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="L101" s="2" t="inlineStr">
         <is>
           <t>哎呀让您踩坑了！不处理这锅我们背，已安排对客服进行培训并由主管1小时内回访您，小客服在线等您验收，祝您接下来体验加分～</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>hybrid-agree</t>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>hybrid-rerank</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K101"/>
+  <autoFilter ref="A1:M101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5823,16 +6845,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>原文</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>预测类别</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>置信度</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>归因</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>语气很冲，好像我欠他钱一样 不会再买了</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>质量差</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>质量差</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>语气很冲，好像我欠他钱一样 不会再买了</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>语气很冲，好像我欠他钱一样 不会再买了</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>质量差</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>质量差</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>语气很冲，好像我欠他钱一样 不会再买了</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>味道很重，晾了三天还有甲醛味</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>质量差</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>甲醛</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>味道很重，晾了三天还有甲醛味</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>语气很冲，好像我欠他钱一样</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>质量差</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>质量差</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>语气很冲，好像我欠他钱一样</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>指标</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>值</t>
         </is>
@@ -5856,7 +7036,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"质量差": 25, "客服态度差": 20, "物流慢": 25, "货不对版": 30}</t>
+          <t>{"质量差": 23, "客服态度差": 19, "物流慢": 25, "货不对版": 33}</t>
         </is>
       </c>
     </row>
@@ -5880,31 +7060,65 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>89.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>耗时(s)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>10.83</t>
-        </is>
+          <t>置信度阈值</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>需人工复核</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4条 (4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>归因方式</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>关键词约束</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>耗时(s)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>37.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>平均(s/条)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.108</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.376</t>
         </is>
       </c>
     </row>
